--- a/data/trans_bre/KIDM_C_3_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/KIDM_C_3_R-Habitat-trans_bre.xlsx
@@ -660,37 +660,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,25; 7,4</t>
+          <t>-6,91; 6,87</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 15,77</t>
+          <t>-2,11; 15,86</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-12,53; 3,48</t>
+          <t>-13,32; 3,89</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-11,98; 3,15</t>
+          <t>-10,69; 3,94</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-69,44; 280,13</t>
+          <t>-77,13; 220,02</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-19,01; 412,05</t>
+          <t>-24,29; 388,58</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-82,2; 68,66</t>
+          <t>-84,28; 76,79</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -760,37 +760,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 8,14</t>
+          <t>-2,53; 7,54</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-15,55; 1,5</t>
+          <t>-14,37; 1,41</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-10,47; 2,0</t>
+          <t>-10,41; 2,37</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,57; 13,69</t>
+          <t>1,46; 13,19</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-46,2; 505,45</t>
+          <t>-51,85; 468,73</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-64,68; 12,17</t>
+          <t>-62,04; 11,27</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-67,96; 27,24</t>
+          <t>-67,47; 32,5</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -860,37 +860,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 8,01</t>
+          <t>-2,94; 8,52</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,44; 20,02</t>
+          <t>0,54; 20,12</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-9,28; 7,53</t>
+          <t>-8,99; 7,74</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 6,29</t>
+          <t>-1,3; 6,25</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-80,53; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,66; 369,64</t>
+          <t>-5,78; 307,06</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-66,66; 145,11</t>
+          <t>-64,7; 137,87</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -960,37 +960,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,63; 5,46</t>
+          <t>-4,58; 5,6</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 16,82</t>
+          <t>-1,52; 14,88</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 10,96</t>
+          <t>-2,75; 11,95</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-5,64; 6,51</t>
+          <t>-6,48; 7,01</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-85,15; 390,17</t>
+          <t>-80,99; 419,5</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-8,38; 356,58</t>
+          <t>-21,6; 278,09</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-30,71; 247,39</t>
+          <t>-30,85; 268,46</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 4,05</t>
+          <t>-1,46; 4,06</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 7,88</t>
+          <t>-0,94; 8,2</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,68; 2,94</t>
+          <t>-4,86; 2,84</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 5,1</t>
+          <t>-0,88; 4,91</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-25,9; 139,95</t>
+          <t>-28,08; 142,54</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-7,65; 77,65</t>
+          <t>-7,3; 85,02</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-38,98; 36,91</t>
+          <t>-42,29; 34,79</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-36,27; 561,79</t>
+          <t>-38,01; 569,29</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/KIDM_C_3_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/KIDM_C_3_R-Habitat-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores de los que se han reido mucho o muchísimo otros menores (autopercepción menor)</t>
+          <t>Menores de los/as que se han reído mucho o muchísimo otros/as menores (autopercepción menor)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -660,37 +660,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,91; 6,87</t>
+          <t>-6,49; 7,26</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 15,86</t>
+          <t>-1,55; 15,85</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-13,32; 3,89</t>
+          <t>-13,59; 3,61</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-10,69; 3,94</t>
+          <t>-11,99; 3,12</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-77,13; 220,02</t>
+          <t>-73,71; 239,52</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-24,29; 388,58</t>
+          <t>-22,49; 442,11</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-84,28; 76,79</t>
+          <t>-83,37; 85,7</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -760,37 +760,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 7,54</t>
+          <t>-2,31; 7,66</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-14,37; 1,41</t>
+          <t>-15,12; 1,97</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-10,41; 2,37</t>
+          <t>-10,81; 1,98</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,46; 13,19</t>
+          <t>1,43; 13,94</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-51,85; 468,73</t>
+          <t>-45,12; 431,02</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-62,04; 11,27</t>
+          <t>-63,1; 14,77</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-67,47; 32,5</t>
+          <t>-68,79; 24,7</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -860,37 +860,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 8,52</t>
+          <t>-2,72; 8,17</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,54; 20,12</t>
+          <t>0,23; 20,31</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,99; 7,74</t>
+          <t>-8,95; 7,58</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 6,25</t>
+          <t>-1,24; 6,99</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-80,53; —</t>
+          <t>-81,47; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,78; 307,06</t>
+          <t>-3,91; 326,44</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-64,7; 137,87</t>
+          <t>-61,9; 125,37</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -960,37 +960,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,58; 5,6</t>
+          <t>-4,48; 5,39</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 14,88</t>
+          <t>-0,99; 16,3</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 11,95</t>
+          <t>-3,08; 11,03</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-6,48; 7,01</t>
+          <t>-6,68; 6,89</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-80,99; 419,5</t>
+          <t>-80,63; 360,13</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-21,6; 278,09</t>
+          <t>-13,6; 321,1</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-30,85; 268,46</t>
+          <t>-32,61; 249,45</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 4,06</t>
+          <t>-1,51; 4,09</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 8,2</t>
+          <t>-0,73; 7,92</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,86; 2,84</t>
+          <t>-4,68; 2,76</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 4,91</t>
+          <t>-0,71; 5,08</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-28,08; 142,54</t>
+          <t>-30,37; 149,17</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-7,3; 85,02</t>
+          <t>-5,5; 83,38</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-42,29; 34,79</t>
+          <t>-39,86; 34,45</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-38,01; 569,29</t>
+          <t>-31,76; 617,21</t>
         </is>
       </c>
     </row>
